--- a/SuppXLS/Scen_UC_DECEL_DECEHEAT_20_50.xlsx
+++ b/SuppXLS/Scen_UC_DECEL_DECEHEAT_20_50.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F44E27BD-75EC-41FD-8D60-F3F25F76789A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{449EF702-9314-4A38-9F0B-621A338E8CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33315" yWindow="2955" windowWidth="21600" windowHeight="11235" xr2:uid="{12993743-A3C9-4B22-8ADD-D2910F70577E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{12993743-A3C9-4B22-8ADD-D2910F70577E}"/>
   </bookViews>
   <sheets>
     <sheet name="DECELC_DECEHEAT_20_50" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
   <si>
     <t>UC - Each Region/Period</t>
   </si>
@@ -105,6 +105,12 @@
   </si>
   <si>
     <t>DECEHEAT</t>
+  </si>
+  <si>
+    <t>HEAT</t>
+  </si>
+  <si>
+    <t>UC_COMPRD</t>
   </si>
 </sst>
 </file>
@@ -690,10 +696,16 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
         <v>18</v>
       </c>
       <c r="G6" t="s">
         <v>22</v>
+      </c>
+      <c r="H6" t="s">
+        <v>24</v>
       </c>
       <c r="I6">
         <v>2030</v>
@@ -722,10 +734,16 @@
         <v>21</v>
       </c>
       <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
         <v>18</v>
       </c>
       <c r="G7" t="s">
         <v>22</v>
+      </c>
+      <c r="H7" t="s">
+        <v>24</v>
       </c>
       <c r="I7">
         <v>2050</v>
